--- a/app/inputs/parameter_template_test.xlsx
+++ b/app/inputs/parameter_template_test.xlsx
@@ -2841,7 +2841,7 @@
         <v>46321</v>
       </c>
       <c r="C28" s="7">
-        <v>46296</v>
+        <v>46327</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
